--- a/events/Samarkand_2024_WCH/Samarkand_2024_WCH_Results.xlsx
+++ b/events/Samarkand_2024_WCH/Samarkand_2024_WCH_Results.xlsx
@@ -12105,6 +12105,11 @@
       <c r="L174" t="n">
         <v>2</v>
       </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
       <c r="X174" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -14856,6 +14861,11 @@
           <t>63767</t>
         </is>
       </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -27580,6 +27590,11 @@
           <t>63767</t>
         </is>
       </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
       <c r="T407" t="inlineStr">
         <is>
           <t>44341</t>
@@ -28598,6 +28613,11 @@
           <t>61143</t>
         </is>
       </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>97342</t>
+        </is>
+      </c>
       <c r="X420" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -40049,6 +40069,11 @@
           <t>63767</t>
         </is>
       </c>
+      <c r="S589" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -43582,6 +43607,11 @@
       <c r="R640" t="inlineStr">
         <is>
           <t>63767</t>
+        </is>
+      </c>
+      <c r="S640" t="inlineStr">
+        <is>
+          <t>42444</t>
         </is>
       </c>
       <c r="T640" t="inlineStr">
@@ -50668,7 +50698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D278"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56787,6 +56817,72 @@
         </is>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Yarisleidis</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>CIRILO DUBOYS</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Anja</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>OSTERMAN</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>97342</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Khamzoda</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>ERKINOVA</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Samarkand_2024_WCH/Samarkand_2024_WCH_Results.xlsx
+++ b/events/Samarkand_2024_WCH/Samarkand_2024_WCH_Results.xlsx
@@ -4195,6 +4195,16 @@
           <t>00:03:45.655</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>123004</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>118519</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -24319,6 +24329,11 @@
           <t>00:00:37.881</t>
         </is>
       </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>147940</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -24729,6 +24744,11 @@
           <t>00:00:54.153</t>
         </is>
       </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>147952</t>
+        </is>
+      </c>
       <c r="S365" t="inlineStr">
         <is>
           <t>147953</t>
@@ -26232,6 +26252,11 @@
       <c r="L388" t="n">
         <v>3</v>
       </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>52787</t>
+        </is>
+      </c>
       <c r="X388" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -28224,6 +28249,11 @@
           <t>147955</t>
         </is>
       </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>147952</t>
+        </is>
+      </c>
       <c r="U415" t="inlineStr">
         <is>
           <t>147956</t>
@@ -28539,6 +28569,11 @@
           <t>98922</t>
         </is>
       </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>133078</t>
+        </is>
+      </c>
       <c r="T419" t="inlineStr">
         <is>
           <t>72642</t>
@@ -31115,6 +31150,16 @@
           <t>00:04:58.003</t>
         </is>
       </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>123004</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>118519</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -32863,6 +32908,11 @@
           <t>00:00:37.704</t>
         </is>
       </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>147940</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -34368,6 +34418,11 @@
           <t>00:00:53.068</t>
         </is>
       </c>
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>147952</t>
+        </is>
+      </c>
       <c r="S505" t="inlineStr">
         <is>
           <t>147953</t>
@@ -44341,6 +44396,11 @@
           <t>98922</t>
         </is>
       </c>
+      <c r="S649" t="inlineStr">
+        <is>
+          <t>133078</t>
+        </is>
+      </c>
       <c r="T649" t="inlineStr">
         <is>
           <t>72642</t>
@@ -47613,6 +47673,11 @@
           <t>00:28:57.638</t>
         </is>
       </c>
+      <c r="R697" t="inlineStr">
+        <is>
+          <t>94174</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -47852,6 +47917,11 @@
       </c>
       <c r="L701" t="n">
         <v>10</v>
+      </c>
+      <c r="R701" t="inlineStr">
+        <is>
+          <t>147295</t>
+        </is>
       </c>
       <c r="X701" t="inlineStr">
         <is>
@@ -50698,7 +50768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D281"/>
+  <dimension ref="A1:D288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56883,6 +56953,160 @@
         </is>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>52787</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Adel</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>MOJALLALIMOGHADAM</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>94174</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Mukhammadi</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>RAJABOV</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>118519</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Kamronbek</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>AKHTAMOV</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>123004</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Mirjalol</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>KAMILOV</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>147295</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Janus</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>ERCILLA</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>147940</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Dilmurod</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>SHERMURODOV</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>147952</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Masuma</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>YADAV</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Samarkand_2024_WCH/Samarkand_2024_WCH_Results.xlsx
+++ b/events/Samarkand_2024_WCH/Samarkand_2024_WCH_Results.xlsx
@@ -27550,6 +27550,11 @@
           <t>77306</t>
         </is>
       </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>97611</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -43595,6 +43600,11 @@
       <c r="T639" t="inlineStr">
         <is>
           <t>77306</t>
+        </is>
+      </c>
+      <c r="U639" t="inlineStr">
+        <is>
+          <t>97611</t>
         </is>
       </c>
     </row>
@@ -50768,7 +50778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D288"/>
+  <dimension ref="A1:D289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57107,6 +57117,28 @@
         </is>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>97611</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Gergely</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>BALOGH</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Samarkand_2024_WCH/Samarkand_2024_WCH_Results.xlsx
+++ b/events/Samarkand_2024_WCH/Samarkand_2024_WCH_Results.xlsx
@@ -57125,7 +57125,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Gergely</t>
+          <t>Gagely</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
